--- a/relationship_surveys/015_marriage_readiness_assessment_form--relationship_surveys.xlsx
+++ b/relationship_surveys/015_marriage_readiness_assessment_form--relationship_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1182,8 +1182,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'In a relationship'}</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'3_months'}</t>
+          <t>3_months</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '3 months'}</t>
+          <t>3 months</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'6-12_months'}</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '6-12 months'}</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'1_year_or_more'}</t>
+          <t>1_year_or_more</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '1 year or more'}</t>
+          <t>1 year or more</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
